--- a/AAAGameData/DataTables/Text/LocalizationTextTable_Misc.xlsx
+++ b/AAAGameData/DataTables/Text/LocalizationTextTable_Misc.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8200"/>
+    <workbookView windowWidth="25600" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="99">
   <si>
     <t>#</t>
   </si>
@@ -100,6 +100,249 @@
   </si>
   <si>
     <t>MiscText.Tech.Researched</t>
+  </si>
+  <si>
+    <t>顶部条增加金币提示</t>
+  </si>
+  <si>
+    <t>UITopbar_AddCoinToast</t>
+  </si>
+  <si>
+    <t>MiscText.UITopbar.AddCoinToast</t>
+  </si>
+  <si>
+    <t>顶部条增加钻石提示</t>
+  </si>
+  <si>
+    <t>UITopbar_AddGemToast</t>
+  </si>
+  <si>
+    <t>MiscText.UITopbar.AddGemToast</t>
+  </si>
+  <si>
+    <t>顶部条增加能量提示</t>
+  </si>
+  <si>
+    <t>UITopbar_AddEnergyToast</t>
+  </si>
+  <si>
+    <t>MiscText.UITopbar.AddEnergyToast</t>
+  </si>
+  <si>
+    <t>关卡目标标题</t>
+  </si>
+  <si>
+    <t>GameEnd_LevelObjective_Title</t>
+  </si>
+  <si>
+    <t>MiscText.GameEnd.LevelObjective.Title</t>
+  </si>
+  <si>
+    <t>关卡目标占领倒计天数</t>
+  </si>
+  <si>
+    <t>GameEnd_Objective_OccupyBeforeDay</t>
+  </si>
+  <si>
+    <t>MiscText.GameEnd.Objective.OccupyBeforeDay</t>
+  </si>
+  <si>
+    <t>关卡目标占领建筑</t>
+  </si>
+  <si>
+    <t>GameEnd_Objective_Occupy</t>
+  </si>
+  <si>
+    <t>MiscText.GameEnd.Objective.Occupy</t>
+  </si>
+  <si>
+    <t>关卡目标生存到天数</t>
+  </si>
+  <si>
+    <t>GameEnd_Objective_SurviveToDay</t>
+  </si>
+  <si>
+    <t>MiscText.GameEnd.Objective.SurviveToDay</t>
+  </si>
+  <si>
+    <t>关卡目标保护基地</t>
+  </si>
+  <si>
+    <t>GameEnd_Objective_DefendBase</t>
+  </si>
+  <si>
+    <t>MiscText.GameEnd.Objective.DefendBase</t>
+  </si>
+  <si>
+    <t>阶段切换阻止标题</t>
+  </si>
+  <si>
+    <t>PhaseSwitch_Blocked_Title</t>
+  </si>
+  <si>
+    <t>MiscText.PhaseSwitch.Blocked.Title</t>
+  </si>
+  <si>
+    <t>阶段切换阻止内容</t>
+  </si>
+  <si>
+    <t>PhaseSwitch_Blocked_Content</t>
+  </si>
+  <si>
+    <t>MiscText.PhaseSwitch.Blocked.Content</t>
+  </si>
+  <si>
+    <t>阶段信息格式</t>
+  </si>
+  <si>
+    <t>PhaseSwitch_DayPhase_Format</t>
+  </si>
+  <si>
+    <t>MiscText.PhaseSwitch.DayPhase.Format</t>
+  </si>
+  <si>
+    <t>阶段名运营</t>
+  </si>
+  <si>
+    <t>PhaseSwitch_Phase_Build</t>
+  </si>
+  <si>
+    <t>MiscText.PhaseSwitch.Phase.Build</t>
+  </si>
+  <si>
+    <t>阶段名战斗</t>
+  </si>
+  <si>
+    <t>PhaseSwitch_Phase_Invade</t>
+  </si>
+  <si>
+    <t>MiscText.PhaseSwitch.Phase.Invade</t>
+  </si>
+  <si>
+    <t>阶段名防御</t>
+  </si>
+  <si>
+    <t>PhaseSwitch_Phase_Defend</t>
+  </si>
+  <si>
+    <t>MiscText.PhaseSwitch.Phase.Defend</t>
+  </si>
+  <si>
+    <t>引导移动标题</t>
+  </si>
+  <si>
+    <t>Tutorial_MoveHero_Title</t>
+  </si>
+  <si>
+    <t>MiscText.Tutorial.MoveHero.Title</t>
+  </si>
+  <si>
+    <t>引导移动内容</t>
+  </si>
+  <si>
+    <t>Tutorial_MoveHero_Content</t>
+  </si>
+  <si>
+    <t>MiscText.Tutorial.MoveHero.Content</t>
+  </si>
+  <si>
+    <t>科技详情基地等级条件</t>
+  </si>
+  <si>
+    <t>TechDetail_Condition_BaseLevel</t>
+  </si>
+  <si>
+    <t>MiscText.TechDetail.Condition.BaseLevel</t>
+  </si>
+  <si>
+    <t>科技详情前置科技条件</t>
+  </si>
+  <si>
+    <t>TechDetail_Condition_PrereqTech</t>
+  </si>
+  <si>
+    <t>MiscText.TechDetail.Condition.PrereqTech</t>
+  </si>
+  <si>
+    <t>科技详情满足其一提示</t>
+  </si>
+  <si>
+    <t>TechDetail_Condition_AnyOf</t>
+  </si>
+  <si>
+    <t>MiscText.TechDetail.Condition.AnyOf</t>
+  </si>
+  <si>
+    <t>科技详情解锁科技描述</t>
+  </si>
+  <si>
+    <t>TechDetail_Unlock_Tech</t>
+  </si>
+  <si>
+    <t>MiscText.TechDetail.Unlock.Tech</t>
+  </si>
+  <si>
+    <t>科技详情持有能力描述</t>
+  </si>
+  <si>
+    <t>TechDetail_Unlock_Capability</t>
+  </si>
+  <si>
+    <t>MiscText.TechDetail.Unlock.Capability</t>
+  </si>
+  <si>
+    <t>科技详情基地等级解锁描述</t>
+  </si>
+  <si>
+    <t>TechDetail_Unlock_BaseLevel</t>
+  </si>
+  <si>
+    <t>MiscText.TechDetail.Unlock.BaseLevel</t>
+  </si>
+  <si>
+    <t>人口显示格式</t>
+  </si>
+  <si>
+    <t>Supply_CurrentMax</t>
+  </si>
+  <si>
+    <t>MiscText.Supply.CurrentMax</t>
+  </si>
+  <si>
+    <t>资源增加提示</t>
+  </si>
+  <si>
+    <t>ResourceModify_Add</t>
+  </si>
+  <si>
+    <t>MiscText.ResourceModify.Add</t>
+  </si>
+  <si>
+    <t>资源减少提示</t>
+  </si>
+  <si>
+    <t>ResourceModify_Reduce</t>
+  </si>
+  <si>
+    <t>MiscText.ResourceModify.Reduce</t>
+  </si>
+  <si>
+    <t>物品增加提示</t>
+  </si>
+  <si>
+    <t>ItemModify_Add</t>
+  </si>
+  <si>
+    <t>MiscText.ItemModify.Add</t>
+  </si>
+  <si>
+    <t>物品减少提示</t>
+  </si>
+  <si>
+    <t>ItemModify_Reduce</t>
+  </si>
+  <si>
+    <t>MiscText.ItemModify.Reduce</t>
   </si>
 </sst>
 </file>
@@ -1052,8 +1295,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.75" outlineLevelRow="5" outlineLevelCol="4"/>
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.75" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="2.5" style="1" customWidth="1"/>
     <col min="2" max="2" width="10.5833333333333" style="1" customWidth="1"/>
@@ -1116,7 +1359,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" ht="17" customHeight="1" spans="2:5">
+    <row r="5" ht="17" customHeight="1" spans="1:5">
       <c r="B5" s="1">
         <v>1</v>
       </c>
@@ -1130,7 +1373,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1" spans="2:5">
+    <row r="6" ht="16" customHeight="1" spans="1:5">
       <c r="B6" s="1">
         <v>2</v>
       </c>
@@ -1142,6 +1385,384 @@
       </c>
       <c r="E6" s="1" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="7" ht="28.75" spans="1:5">
+      <c r="B7" s="1">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" ht="28.75" spans="1:5">
+      <c r="B8" s="1">
+        <v>4</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" ht="28.75" spans="1:5">
+      <c r="B9" s="1">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" ht="28.75" spans="1:5">
+      <c r="B10" s="1">
+        <v>6</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" ht="28.75" spans="1:5">
+      <c r="B11" s="1">
+        <v>7</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" ht="28.75" spans="1:5">
+      <c r="B12" s="1">
+        <v>8</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" ht="28.75" spans="1:5">
+      <c r="B13" s="1">
+        <v>9</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" ht="28.75" spans="1:5">
+      <c r="B14" s="1">
+        <v>10</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" ht="28.75" spans="1:5">
+      <c r="B15" s="1">
+        <v>11</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" ht="28.75" spans="1:5">
+      <c r="B16" s="1">
+        <v>12</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" ht="28.75" spans="2:5">
+      <c r="B17" s="1">
+        <v>13</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" ht="28.75" spans="2:5">
+      <c r="B18" s="1">
+        <v>14</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" ht="28.75" spans="2:5">
+      <c r="B19" s="1">
+        <v>15</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" ht="28.75" spans="2:5">
+      <c r="B20" s="1">
+        <v>16</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" ht="28.75" spans="2:5">
+      <c r="B21" s="1">
+        <v>17</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" ht="28.75" spans="2:5">
+      <c r="B22" s="1">
+        <v>18</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" ht="28.75" spans="2:5">
+      <c r="B23" s="1">
+        <v>19</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="24" ht="28.75" spans="2:5">
+      <c r="B24" s="1">
+        <v>20</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" ht="28.75" spans="2:5">
+      <c r="B25" s="1">
+        <v>21</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26" ht="28.75" spans="2:5">
+      <c r="B26" s="1">
+        <v>22</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" ht="28.75" spans="2:5">
+      <c r="B27" s="1">
+        <v>23</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" ht="28.75" spans="2:5">
+      <c r="B28" s="1">
+        <v>24</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5">
+      <c r="B29" s="1">
+        <v>25</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5">
+      <c r="B30" s="1">
+        <v>26</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="31" ht="28.75" spans="2:5">
+      <c r="B31" s="1">
+        <v>27</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5">
+      <c r="B32" s="1">
+        <v>28</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5">
+      <c r="B33" s="1">
+        <v>29</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/Text/LocalizationTextTable_Misc.xlsx
+++ b/AAAGameData/DataTables/Text/LocalizationTextTable_Misc.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="10480"/>
+    <workbookView windowWidth="19200" windowHeight="8200"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
   <si>
     <t>#</t>
   </si>
@@ -84,61 +84,7 @@
     <t>选项文本(多语言)</t>
   </si>
   <si>
-    <t>科技节点研究按钮</t>
-  </si>
-  <si>
-    <t>Tech_Research</t>
-  </si>
-  <si>
-    <t>MiscText.Tech.Research</t>
-  </si>
-  <si>
-    <t>科技节点已研究按钮</t>
-  </si>
-  <si>
-    <t>Tech_Researched</t>
-  </si>
-  <si>
-    <t>MiscText.Tech.Researched</t>
-  </si>
-  <si>
-    <t>顶部条增加金币提示</t>
-  </si>
-  <si>
-    <t>UITopbar_AddCoinToast</t>
-  </si>
-  <si>
-    <t>MiscText.UITopbar.AddCoinToast</t>
-  </si>
-  <si>
-    <t>顶部条增加钻石提示</t>
-  </si>
-  <si>
-    <t>UITopbar_AddGemToast</t>
-  </si>
-  <si>
-    <t>MiscText.UITopbar.AddGemToast</t>
-  </si>
-  <si>
-    <t>顶部条增加能量提示</t>
-  </si>
-  <si>
-    <t>UITopbar_AddEnergyToast</t>
-  </si>
-  <si>
-    <t>MiscText.UITopbar.AddEnergyToast</t>
-  </si>
-  <si>
-    <t>关卡目标标题</t>
-  </si>
-  <si>
-    <t>GameEnd_LevelObjective_Title</t>
-  </si>
-  <si>
-    <t>MiscText.GameEnd.LevelObjective.Title</t>
-  </si>
-  <si>
-    <t>关卡目标占领倒计天数</t>
+    <t>行动目标_占领倒计天数</t>
   </si>
   <si>
     <t>GameEnd_Objective_OccupyBeforeDay</t>
@@ -147,7 +93,7 @@
     <t>MiscText.GameEnd.Objective.OccupyBeforeDay</t>
   </si>
   <si>
-    <t>关卡目标占领建筑</t>
+    <t>行动目标_占领建筑</t>
   </si>
   <si>
     <t>GameEnd_Objective_Occupy</t>
@@ -156,7 +102,7 @@
     <t>MiscText.GameEnd.Objective.Occupy</t>
   </si>
   <si>
-    <t>关卡目标生存到天数</t>
+    <t>行动目标_生存天数</t>
   </si>
   <si>
     <t>GameEnd_Objective_SurviveToDay</t>
@@ -165,7 +111,7 @@
     <t>MiscText.GameEnd.Objective.SurviveToDay</t>
   </si>
   <si>
-    <t>关卡目标保护基地</t>
+    <t>行动目标_保护基地</t>
   </si>
   <si>
     <t>GameEnd_Objective_DefendBase</t>
@@ -174,34 +120,7 @@
     <t>MiscText.GameEnd.Objective.DefendBase</t>
   </si>
   <si>
-    <t>阶段切换阻止标题</t>
-  </si>
-  <si>
-    <t>PhaseSwitch_Blocked_Title</t>
-  </si>
-  <si>
-    <t>MiscText.PhaseSwitch.Blocked.Title</t>
-  </si>
-  <si>
-    <t>阶段切换阻止内容</t>
-  </si>
-  <si>
-    <t>PhaseSwitch_Blocked_Content</t>
-  </si>
-  <si>
-    <t>MiscText.PhaseSwitch.Blocked.Content</t>
-  </si>
-  <si>
-    <t>阶段信息格式</t>
-  </si>
-  <si>
-    <t>PhaseSwitch_DayPhase_Format</t>
-  </si>
-  <si>
-    <t>MiscText.PhaseSwitch.DayPhase.Format</t>
-  </si>
-  <si>
-    <t>阶段名运营</t>
+    <t>阶段名_运营</t>
   </si>
   <si>
     <t>PhaseSwitch_Phase_Build</t>
@@ -210,7 +129,7 @@
     <t>MiscText.PhaseSwitch.Phase.Build</t>
   </si>
   <si>
-    <t>阶段名战斗</t>
+    <t>阶段名_进攻</t>
   </si>
   <si>
     <t>PhaseSwitch_Phase_Invade</t>
@@ -219,130 +138,13 @@
     <t>MiscText.PhaseSwitch.Phase.Invade</t>
   </si>
   <si>
-    <t>阶段名防御</t>
+    <t>阶段名_防御</t>
   </si>
   <si>
     <t>PhaseSwitch_Phase_Defend</t>
   </si>
   <si>
     <t>MiscText.PhaseSwitch.Phase.Defend</t>
-  </si>
-  <si>
-    <t>引导移动标题</t>
-  </si>
-  <si>
-    <t>Tutorial_MoveHero_Title</t>
-  </si>
-  <si>
-    <t>MiscText.Tutorial.MoveHero.Title</t>
-  </si>
-  <si>
-    <t>引导移动内容</t>
-  </si>
-  <si>
-    <t>Tutorial_MoveHero_Content</t>
-  </si>
-  <si>
-    <t>MiscText.Tutorial.MoveHero.Content</t>
-  </si>
-  <si>
-    <t>科技详情基地等级条件</t>
-  </si>
-  <si>
-    <t>TechDetail_Condition_BaseLevel</t>
-  </si>
-  <si>
-    <t>MiscText.TechDetail.Condition.BaseLevel</t>
-  </si>
-  <si>
-    <t>科技详情前置科技条件</t>
-  </si>
-  <si>
-    <t>TechDetail_Condition_PrereqTech</t>
-  </si>
-  <si>
-    <t>MiscText.TechDetail.Condition.PrereqTech</t>
-  </si>
-  <si>
-    <t>科技详情满足其一提示</t>
-  </si>
-  <si>
-    <t>TechDetail_Condition_AnyOf</t>
-  </si>
-  <si>
-    <t>MiscText.TechDetail.Condition.AnyOf</t>
-  </si>
-  <si>
-    <t>科技详情解锁科技描述</t>
-  </si>
-  <si>
-    <t>TechDetail_Unlock_Tech</t>
-  </si>
-  <si>
-    <t>MiscText.TechDetail.Unlock.Tech</t>
-  </si>
-  <si>
-    <t>科技详情持有能力描述</t>
-  </si>
-  <si>
-    <t>TechDetail_Unlock_Capability</t>
-  </si>
-  <si>
-    <t>MiscText.TechDetail.Unlock.Capability</t>
-  </si>
-  <si>
-    <t>科技详情基地等级解锁描述</t>
-  </si>
-  <si>
-    <t>TechDetail_Unlock_BaseLevel</t>
-  </si>
-  <si>
-    <t>MiscText.TechDetail.Unlock.BaseLevel</t>
-  </si>
-  <si>
-    <t>人口显示格式</t>
-  </si>
-  <si>
-    <t>Supply_CurrentMax</t>
-  </si>
-  <si>
-    <t>MiscText.Supply.CurrentMax</t>
-  </si>
-  <si>
-    <t>资源增加提示</t>
-  </si>
-  <si>
-    <t>ResourceModify_Add</t>
-  </si>
-  <si>
-    <t>MiscText.ResourceModify.Add</t>
-  </si>
-  <si>
-    <t>资源减少提示</t>
-  </si>
-  <si>
-    <t>ResourceModify_Reduce</t>
-  </si>
-  <si>
-    <t>MiscText.ResourceModify.Reduce</t>
-  </si>
-  <si>
-    <t>物品增加提示</t>
-  </si>
-  <si>
-    <t>ItemModify_Add</t>
-  </si>
-  <si>
-    <t>MiscText.ItemModify.Add</t>
-  </si>
-  <si>
-    <t>物品减少提示</t>
-  </si>
-  <si>
-    <t>ItemModify_Reduce</t>
-  </si>
-  <si>
-    <t>MiscText.ItemModify.Reduce</t>
   </si>
 </sst>
 </file>
@@ -1295,7 +1097,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.75" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="2.5" style="1" customWidth="1"/>
@@ -1359,7 +1161,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" ht="17" customHeight="1" spans="1:5">
+    <row r="5" ht="33" customHeight="1" spans="2:5">
       <c r="B5" s="1">
         <v>1</v>
       </c>
@@ -1373,7 +1175,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1" spans="1:5">
+    <row r="6" ht="16" customHeight="1" spans="2:5">
       <c r="B6" s="1">
         <v>2</v>
       </c>
@@ -1387,7 +1189,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" ht="28.75" spans="1:5">
+    <row r="7" ht="28.75" spans="2:5">
       <c r="B7" s="1">
         <v>3</v>
       </c>
@@ -1401,7 +1203,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" ht="28.75" spans="1:5">
+    <row r="8" ht="28.75" spans="2:5">
       <c r="B8" s="1">
         <v>4</v>
       </c>
@@ -1415,7 +1217,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" ht="28.75" spans="1:5">
+    <row r="9" ht="28.75" spans="2:5">
       <c r="B9" s="1">
         <v>5</v>
       </c>
@@ -1429,7 +1231,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" ht="28.75" spans="1:5">
+    <row r="10" ht="28.75" spans="2:5">
       <c r="B10" s="1">
         <v>6</v>
       </c>
@@ -1443,7 +1245,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" ht="28.75" spans="1:5">
+    <row r="11" ht="28.75" spans="2:5">
       <c r="B11" s="1">
         <v>7</v>
       </c>
@@ -1455,314 +1257,6 @@
       </c>
       <c r="E11" s="1" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="12" ht="28.75" spans="1:5">
-      <c r="B12" s="1">
-        <v>8</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" ht="28.75" spans="1:5">
-      <c r="B13" s="1">
-        <v>9</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" ht="28.75" spans="1:5">
-      <c r="B14" s="1">
-        <v>10</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" ht="28.75" spans="1:5">
-      <c r="B15" s="1">
-        <v>11</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" ht="28.75" spans="1:5">
-      <c r="B16" s="1">
-        <v>12</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" ht="28.75" spans="2:5">
-      <c r="B17" s="1">
-        <v>13</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" ht="28.75" spans="2:5">
-      <c r="B18" s="1">
-        <v>14</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="19" ht="28.75" spans="2:5">
-      <c r="B19" s="1">
-        <v>15</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="20" ht="28.75" spans="2:5">
-      <c r="B20" s="1">
-        <v>16</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="21" ht="28.75" spans="2:5">
-      <c r="B21" s="1">
-        <v>17</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="22" ht="28.75" spans="2:5">
-      <c r="B22" s="1">
-        <v>18</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="23" ht="28.75" spans="2:5">
-      <c r="B23" s="1">
-        <v>19</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="24" ht="28.75" spans="2:5">
-      <c r="B24" s="1">
-        <v>20</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25" ht="28.75" spans="2:5">
-      <c r="B25" s="1">
-        <v>21</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="26" ht="28.75" spans="2:5">
-      <c r="B26" s="1">
-        <v>22</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="27" ht="28.75" spans="2:5">
-      <c r="B27" s="1">
-        <v>23</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="28" ht="28.75" spans="2:5">
-      <c r="B28" s="1">
-        <v>24</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="29" spans="2:5">
-      <c r="B29" s="1">
-        <v>25</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5">
-      <c r="B30" s="1">
-        <v>26</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="31" ht="28.75" spans="2:5">
-      <c r="B31" s="1">
-        <v>27</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5">
-      <c r="B32" s="1">
-        <v>28</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="33" spans="2:5">
-      <c r="B33" s="1">
-        <v>29</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/Text/LocalizationTextTable_Misc.xlsx
+++ b/AAAGameData/DataTables/Text/LocalizationTextTable_Misc.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8200"/>
+    <workbookView windowWidth="25600" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -87,64 +87,64 @@
     <t>行动目标_占领倒计天数</t>
   </si>
   <si>
-    <t>GameEnd_Objective_OccupyBeforeDay</t>
-  </si>
-  <si>
-    <t>MiscText.GameEnd.Objective.OccupyBeforeDay</t>
+    <t>GameEnd_Cond_OccupyBeforeDay</t>
+  </si>
+  <si>
+    <t>GameEnd.Cond.OccupyBeforeDay</t>
   </si>
   <si>
     <t>行动目标_占领建筑</t>
   </si>
   <si>
-    <t>GameEnd_Objective_Occupy</t>
-  </si>
-  <si>
-    <t>MiscText.GameEnd.Objective.Occupy</t>
+    <t>GameEnd_Cond_Occupy</t>
+  </si>
+  <si>
+    <t>GameEnd.Cond.Occupy</t>
   </si>
   <si>
     <t>行动目标_生存天数</t>
   </si>
   <si>
-    <t>GameEnd_Objective_SurviveToDay</t>
-  </si>
-  <si>
-    <t>MiscText.GameEnd.Objective.SurviveToDay</t>
+    <t>GameEnd_Cond_SurviveToDay</t>
+  </si>
+  <si>
+    <t>GameEnd.Cond.SurviveToDay</t>
   </si>
   <si>
     <t>行动目标_保护基地</t>
   </si>
   <si>
-    <t>GameEnd_Objective_DefendBase</t>
-  </si>
-  <si>
-    <t>MiscText.GameEnd.Objective.DefendBase</t>
+    <t>GameEnd_Cond_DefendBase</t>
+  </si>
+  <si>
+    <t>GameEnd.Cond.DefendBase</t>
   </si>
   <si>
     <t>阶段名_运营</t>
   </si>
   <si>
-    <t>PhaseSwitch_Phase_Build</t>
-  </si>
-  <si>
-    <t>MiscText.PhaseSwitch.Phase.Build</t>
+    <t>Phase_Build</t>
+  </si>
+  <si>
+    <t>Phase.Build</t>
   </si>
   <si>
     <t>阶段名_进攻</t>
   </si>
   <si>
-    <t>PhaseSwitch_Phase_Invade</t>
-  </si>
-  <si>
-    <t>MiscText.PhaseSwitch.Phase.Invade</t>
+    <t>Phase_Invade</t>
+  </si>
+  <si>
+    <t>Phase.Invade</t>
   </si>
   <si>
     <t>阶段名_防御</t>
   </si>
   <si>
-    <t>PhaseSwitch_Phase_Defend</t>
-  </si>
-  <si>
-    <t>MiscText.PhaseSwitch.Phase.Defend</t>
+    <t>Phase_Defend</t>
+  </si>
+  <si>
+    <t>Phase.Defend</t>
   </si>
 </sst>
 </file>
@@ -1161,7 +1161,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" ht="33" customHeight="1" spans="2:5">
+    <row r="5" ht="33" customHeight="1" spans="1:5">
       <c r="B5" s="1">
         <v>1</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1" spans="2:5">
+    <row r="6" ht="32" customHeight="1" spans="1:5">
       <c r="B6" s="1">
         <v>2</v>
       </c>
@@ -1189,7 +1189,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" ht="28.75" spans="2:5">
+    <row r="7" ht="28.75" spans="1:5">
       <c r="B7" s="1">
         <v>3</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" ht="28.75" spans="2:5">
+    <row r="8" ht="28.75" spans="1:5">
       <c r="B8" s="1">
         <v>4</v>
       </c>
@@ -1217,7 +1217,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" ht="28.75" spans="2:5">
+    <row r="9" spans="1:5">
       <c r="B9" s="1">
         <v>5</v>
       </c>
@@ -1231,7 +1231,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" ht="28.75" spans="2:5">
+    <row r="10" spans="1:5">
       <c r="B10" s="1">
         <v>6</v>
       </c>
@@ -1245,7 +1245,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" ht="28.75" spans="2:5">
+    <row r="11" spans="1:5">
       <c r="B11" s="1">
         <v>7</v>
       </c>

--- a/AAAGameData/DataTables/Text/LocalizationTextTable_Misc.xlsx
+++ b/AAAGameData/DataTables/Text/LocalizationTextTable_Misc.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="10480"/>
+    <workbookView windowWidth="18920" windowHeight="9880"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
   <si>
     <t>#</t>
   </si>
@@ -82,6 +82,15 @@
   </si>
   <si>
     <t>选项文本(多语言)</t>
+  </si>
+  <si>
+    <t>行动目标_标题</t>
+  </si>
+  <si>
+    <t>GameEnd_Cond_Title</t>
+  </si>
+  <si>
+    <t>GameEnd.Cond.Title</t>
   </si>
   <si>
     <t>行动目标_占领倒计天数</t>
@@ -1097,7 +1106,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.75" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="2.5" style="1" customWidth="1"/>
@@ -1217,7 +1226,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" ht="28.75" spans="1:5">
       <c r="B9" s="1">
         <v>5</v>
       </c>
@@ -1257,6 +1266,20 @@
       </c>
       <c r="E11" s="1" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="B12" s="1">
+        <v>8</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/Text/LocalizationTextTable_Misc.xlsx
+++ b/AAAGameData/DataTables/Text/LocalizationTextTable_Misc.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18920" windowHeight="9880"/>
+    <workbookView windowWidth="25600" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
   <si>
     <t>#</t>
   </si>
@@ -154,6 +154,33 @@
   </si>
   <si>
     <t>Phase.Defend</t>
+  </si>
+  <si>
+    <t>科技描述_升级已有技能</t>
+  </si>
+  <si>
+    <t>Tech_Desc_SkillAlreadyLearned</t>
+  </si>
+  <si>
+    <t>Tech.Desc.SkillAlreadyLearned</t>
+  </si>
+  <si>
+    <t>科技描述-学习主动技能</t>
+  </si>
+  <si>
+    <t>Tech_Desc_LearnActiveSkill</t>
+  </si>
+  <si>
+    <t>Tech.Desc.LearnActiveSkill</t>
+  </si>
+  <si>
+    <t>科技描述-学习被动技能</t>
+  </si>
+  <si>
+    <t>Tech_Desc_LearnPassiveSkill</t>
+  </si>
+  <si>
+    <t>Tech.Desc.LearnPassiveSkill</t>
   </si>
 </sst>
 </file>
@@ -1106,7 +1133,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.75" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="2.5" style="1" customWidth="1"/>
@@ -1282,6 +1309,48 @@
         <v>35</v>
       </c>
     </row>
+    <row r="13" ht="28.75" spans="1:5">
+      <c r="B13" s="1">
+        <v>9</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" ht="28.75" spans="1:5">
+      <c r="B14" s="1">
+        <v>10</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" ht="28.75" spans="1:5">
+      <c r="B15" s="1">
+        <v>11</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/AAAGameData/DataTables/Text/LocalizationTextTable_Misc.xlsx
+++ b/AAAGameData/DataTables/Text/LocalizationTextTable_Misc.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="10480"/>
+    <workbookView windowWidth="10720" windowHeight="9880"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="51">
   <si>
     <t>#</t>
   </si>
@@ -165,7 +165,7 @@
     <t>Tech.Desc.SkillAlreadyLearned</t>
   </si>
   <si>
-    <t>科技描述-学习主动技能</t>
+    <t>科技描述_学习主动技能</t>
   </si>
   <si>
     <t>Tech_Desc_LearnActiveSkill</t>
@@ -174,13 +174,31 @@
     <t>Tech.Desc.LearnActiveSkill</t>
   </si>
   <si>
-    <t>科技描述-学习被动技能</t>
+    <t>科技描述_学习被动技能</t>
   </si>
   <si>
     <t>Tech_Desc_LearnPassiveSkill</t>
   </si>
   <si>
     <t>Tech.Desc.LearnPassiveSkill</t>
+  </si>
+  <si>
+    <t>建筑升级条件_基地等级</t>
+  </si>
+  <si>
+    <t>Building_Upgrade_Cond_BaseLevel</t>
+  </si>
+  <si>
+    <t>Building.Upgrade.Cond.BaseLevel</t>
+  </si>
+  <si>
+    <t>建筑升级条件_唯一科技</t>
+  </si>
+  <si>
+    <t>Building_Upgrade_Cond_UniqueTech</t>
+  </si>
+  <si>
+    <t>Building.Upgrade.Cond.UniqueTech</t>
   </si>
 </sst>
 </file>
@@ -1133,7 +1151,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.75" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="2.5" style="1" customWidth="1"/>
@@ -1351,6 +1369,34 @@
         <v>44</v>
       </c>
     </row>
+    <row r="16" ht="28.75" spans="1:5">
+      <c r="B16" s="1">
+        <v>12</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" ht="28.75" spans="2:5">
+      <c r="B17" s="1">
+        <v>13</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/AAAGameData/DataTables/Text/LocalizationTextTable_Misc.xlsx
+++ b/AAAGameData/DataTables/Text/LocalizationTextTable_Misc.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="10720" windowHeight="9880"/>
+    <workbookView windowWidth="25600" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="57">
   <si>
     <t>#</t>
   </si>
@@ -199,6 +199,24 @@
   </si>
   <si>
     <t>Building.Upgrade.Cond.UniqueTech</t>
+  </si>
+  <si>
+    <t>关卡tag总称_正面</t>
+  </si>
+  <si>
+    <t>LvTag_Positive</t>
+  </si>
+  <si>
+    <t>LvTag.Positive</t>
+  </si>
+  <si>
+    <t>关卡tag总称_负面</t>
+  </si>
+  <si>
+    <t>LvTag_Negative</t>
+  </si>
+  <si>
+    <t>LvTag.Negative</t>
   </si>
 </sst>
 </file>
@@ -1151,7 +1169,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.75" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="2.5" style="1" customWidth="1"/>
@@ -1397,6 +1415,34 @@
         <v>50</v>
       </c>
     </row>
+    <row r="18" spans="2:5">
+      <c r="B18" s="1">
+        <v>14</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5">
+      <c r="B19" s="1">
+        <v>15</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/AAAGameData/DataTables/Text/LocalizationTextTable_Misc.xlsx
+++ b/AAAGameData/DataTables/Text/LocalizationTextTable_Misc.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="113">
   <si>
     <t>#</t>
   </si>
@@ -53,7 +53,7 @@
     <t>string</t>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -63,7 +63,7 @@
       </rPr>
       <t>s</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -217,6 +217,174 @@
   </si>
   <si>
     <t>LvTag.Negative</t>
+  </si>
+  <si>
+    <t>变量试验名称_标准</t>
+  </si>
+  <si>
+    <t>VariableExperiment_Name_Default</t>
+  </si>
+  <si>
+    <t>变量试验描述_标准</t>
+  </si>
+  <si>
+    <t>VariableExperiment_Desc_Default</t>
+  </si>
+  <si>
+    <t>变量试验名称_一命编程</t>
+  </si>
+  <si>
+    <t>VariableExperiment_Name_OneHealthCoding</t>
+  </si>
+  <si>
+    <t>变量试验描述_一命编程</t>
+  </si>
+  <si>
+    <t>VariableExperiment_Desc_OneHealthCoding</t>
+  </si>
+  <si>
+    <t>局外成长名称_HeroAttack</t>
+  </si>
+  <si>
+    <t>MetaGrowth_Name_HeroAttack</t>
+  </si>
+  <si>
+    <t>局外成长描述_HeroAttack</t>
+  </si>
+  <si>
+    <t>MetaGrowth_Desc_HeroAttack</t>
+  </si>
+  <si>
+    <t>局外成长名称_HeroHealth</t>
+  </si>
+  <si>
+    <t>MetaGrowth_Name_HeroHealth</t>
+  </si>
+  <si>
+    <t>局外成长描述_HeroHealth</t>
+  </si>
+  <si>
+    <t>MetaGrowth_Desc_HeroHealth</t>
+  </si>
+  <si>
+    <t>局外成长名称_UnitAttack</t>
+  </si>
+  <si>
+    <t>MetaGrowth_Name_UnitAttack</t>
+  </si>
+  <si>
+    <t>局外成长描述_UnitAttack</t>
+  </si>
+  <si>
+    <t>MetaGrowth_Desc_UnitAttack</t>
+  </si>
+  <si>
+    <t>局外成长名称_UnitHealth</t>
+  </si>
+  <si>
+    <t>MetaGrowth_Name_UnitHealth</t>
+  </si>
+  <si>
+    <t>局外成长描述_UnitHealth</t>
+  </si>
+  <si>
+    <t>MetaGrowth_Desc_UnitHealth</t>
+  </si>
+  <si>
+    <t>局外成长名称_BuildingAttack</t>
+  </si>
+  <si>
+    <t>MetaGrowth_Name_BuildingAttack</t>
+  </si>
+  <si>
+    <t>局外成长描述_BuildingAttack</t>
+  </si>
+  <si>
+    <t>MetaGrowth_Desc_BuildingAttack</t>
+  </si>
+  <si>
+    <t>局外成长名称_BuildingArmor</t>
+  </si>
+  <si>
+    <t>MetaGrowth_Name_BuildingArmor</t>
+  </si>
+  <si>
+    <t>局外成长描述_BuildingArmor</t>
+  </si>
+  <si>
+    <t>MetaGrowth_Desc_BuildingArmor</t>
+  </si>
+  <si>
+    <t>局外成长名称_BuildingHealth</t>
+  </si>
+  <si>
+    <t>MetaGrowth_Name_BuildingHealth</t>
+  </si>
+  <si>
+    <t>局外成长描述_BuildingHealth</t>
+  </si>
+  <si>
+    <t>MetaGrowth_Desc_BuildingHealth</t>
+  </si>
+  <si>
+    <t>局外成长名称_CoreUpgradeDiscount</t>
+  </si>
+  <si>
+    <t>MetaGrowth_Name_CoreUpgradeDiscount</t>
+  </si>
+  <si>
+    <t>局外成长描述_CoreUpgradeDiscount</t>
+  </si>
+  <si>
+    <t>MetaGrowth_Desc_CoreUpgradeDiscount</t>
+  </si>
+  <si>
+    <t>局外成长名称_PeriodicOrange</t>
+  </si>
+  <si>
+    <t>MetaGrowth_Name_PeriodicOrange</t>
+  </si>
+  <si>
+    <t>局外成长描述_PeriodicOrange</t>
+  </si>
+  <si>
+    <t>MetaGrowth_Desc_PeriodicOrange</t>
+  </si>
+  <si>
+    <t>局外成长名称_InitialOrange</t>
+  </si>
+  <si>
+    <t>MetaGrowth_Name_InitialOrange</t>
+  </si>
+  <si>
+    <t>局外成长描述_InitialOrange</t>
+  </si>
+  <si>
+    <t>MetaGrowth_Desc_InitialOrange</t>
+  </si>
+  <si>
+    <t>局外成长名称_InitialFrequency</t>
+  </si>
+  <si>
+    <t>MetaGrowth_Name_InitialFrequency</t>
+  </si>
+  <si>
+    <t>局外成长描述_InitialFrequency</t>
+  </si>
+  <si>
+    <t>MetaGrowth_Desc_InitialFrequency</t>
+  </si>
+  <si>
+    <t>变量试验名称_地形变体</t>
+  </si>
+  <si>
+    <t>VariableExperiment_Name_VariantTerrain</t>
+  </si>
+  <si>
+    <t>变量试验描述_地形变体</t>
+  </si>
+  <si>
+    <t>VariableExperiment_Desc_VariantTerrain</t>
   </si>
 </sst>
 </file>
@@ -700,154 +868,154 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="1" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="2" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="0" applyFont="0" fillId="2" applyFill="1" borderId="2" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="3" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="4" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="5" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="6" applyFont="1" fillId="0" applyFill="0" borderId="3" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="7" applyFont="1" fillId="0" applyFill="0" borderId="3" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="8" applyFont="1" fillId="0" applyFill="0" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="8" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="3" applyFill="1" borderId="5" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="10" applyFont="1" fillId="4" applyFill="1" borderId="6" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="11" applyFont="1" fillId="4" applyFill="1" borderId="5" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="12" applyFont="1" fillId="5" applyFill="1" borderId="7" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="13" applyFont="1" fillId="0" applyFill="0" borderId="8" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="14" applyFont="1" fillId="0" applyFill="0" borderId="9" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="15" applyFont="1" fillId="6" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="16" applyFont="1" fillId="7" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="17" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="18" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="18" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="18" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="18" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="18" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="18" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="18" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="18" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="18" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="18" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="18" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="18" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1169,18 +1337,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.75" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="2.5" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5833333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.9166666666667" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.8333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="25.4166666666667" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.875" style="1"/>
+    <col min="1" max="1" width="2.5" customWidth="1" style="1"/>
+    <col min="2" max="2" width="10.5833333333333" customWidth="1" style="1"/>
+    <col min="3" max="3" width="18.9166666666667" customWidth="1" style="1"/>
+    <col min="4" max="4" width="19.8333333333333" customWidth="1" style="1"/>
+    <col min="5" max="5" width="25.4166666666667" customWidth="1" style="1"/>
+    <col min="6" max="16384" width="8.875" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.75" spans="1:5">
+    <row r="1" ht="28.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1191,7 +1359,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1205,7 +1373,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1219,7 +1387,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1233,7 +1401,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" ht="33" customHeight="1" spans="1:5">
+    <row r="5" ht="33" customHeight="1">
       <c r="B5" s="1">
         <v>1</v>
       </c>
@@ -1247,7 +1415,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" ht="32" customHeight="1" spans="1:5">
+    <row r="6" ht="32" customHeight="1">
       <c r="B6" s="1">
         <v>2</v>
       </c>
@@ -1261,7 +1429,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" ht="28.75" spans="1:5">
+    <row r="7" ht="28.75">
       <c r="B7" s="1">
         <v>3</v>
       </c>
@@ -1275,7 +1443,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" ht="28.75" spans="1:5">
+    <row r="8" ht="28.75">
       <c r="B8" s="1">
         <v>4</v>
       </c>
@@ -1289,7 +1457,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" ht="28.75" spans="1:5">
+    <row r="9" ht="28.75">
       <c r="B9" s="1">
         <v>5</v>
       </c>
@@ -1303,7 +1471,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10">
       <c r="B10" s="1">
         <v>6</v>
       </c>
@@ -1317,7 +1485,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11">
       <c r="B11" s="1">
         <v>7</v>
       </c>
@@ -1331,7 +1499,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12">
       <c r="B12" s="1">
         <v>8</v>
       </c>
@@ -1345,7 +1513,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" ht="28.75" spans="1:5">
+    <row r="13" ht="28.75">
       <c r="B13" s="1">
         <v>9</v>
       </c>
@@ -1359,7 +1527,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" ht="28.75" spans="1:5">
+    <row r="14" ht="28.75">
       <c r="B14" s="1">
         <v>10</v>
       </c>
@@ -1373,7 +1541,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" ht="28.75" spans="1:5">
+    <row r="15" ht="28.75">
       <c r="B15" s="1">
         <v>11</v>
       </c>
@@ -1387,7 +1555,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" ht="28.75" spans="1:5">
+    <row r="16" ht="28.75">
       <c r="B16" s="1">
         <v>12</v>
       </c>
@@ -1401,7 +1569,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" ht="28.75" spans="2:5">
+    <row r="17" ht="28.75">
       <c r="B17" s="1">
         <v>13</v>
       </c>
@@ -1415,7 +1583,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="2:5">
+    <row r="18">
       <c r="B18" s="1">
         <v>14</v>
       </c>
@@ -1429,7 +1597,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" spans="2:5">
+    <row r="19">
       <c r="B19" s="1">
         <v>15</v>
       </c>
@@ -1441,6 +1609,398 @@
       </c>
       <c r="E19" s="1" t="s">
         <v>56</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="1">
+        <v>16</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="1">
+        <v>17</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="1">
+        <v>18</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="1">
+        <v>19</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="1">
+        <v>20</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="1">
+        <v>21</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="1">
+        <v>22</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="1">
+        <v>23</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="1">
+        <v>24</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="1">
+        <v>25</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="1">
+        <v>26</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="1">
+        <v>27</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="1">
+        <v>28</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="1">
+        <v>29</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="1">
+        <v>30</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="1">
+        <v>31</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="1">
+        <v>32</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="1">
+        <v>33</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="1">
+        <v>34</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="1">
+        <v>35</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="1">
+        <v>36</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="1">
+        <v>37</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="1">
+        <v>38</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="1">
+        <v>39</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="1">
+        <v>40</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="1">
+        <v>41</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="1">
+        <v>42</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="1">
+        <v>43</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/Text/LocalizationTextTable_Misc.xlsx
+++ b/AAAGameData/DataTables/Text/LocalizationTextTable_Misc.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="122">
   <si>
     <t>#</t>
   </si>
@@ -385,6 +385,33 @@
   </si>
   <si>
     <t>VariableExperiment_Desc_VariantTerrain</t>
+  </si>
+  <si>
+    <t>目标栏_主要目标标题</t>
+  </si>
+  <si>
+    <t>GoalUI_PrimaryTitle</t>
+  </si>
+  <si>
+    <t>GoalUI.PrimaryTitle</t>
+  </si>
+  <si>
+    <t>目标栏_可选目标标题</t>
+  </si>
+  <si>
+    <t>GoalUI_OptionalTitle</t>
+  </si>
+  <si>
+    <t>GoalUI.OptionalTitle</t>
+  </si>
+  <si>
+    <t>目标栏_可选目标经验</t>
+  </si>
+  <si>
+    <t>GoalUI_OptionalExperience</t>
+  </si>
+  <si>
+    <t>GoalUI.OptionalExperience</t>
   </si>
 </sst>
 </file>
@@ -1337,7 +1364,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.75" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1" style="1"/>
@@ -2003,6 +2030,51 @@
         <v>112</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1">
+        <v>44</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1">
+        <v>45</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1">
+        <v>46</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/AAAGameData/DataTables/Text/LocalizationTextTable_Misc.xlsx
+++ b/AAAGameData/DataTables/Text/LocalizationTextTable_Misc.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="168">
   <si>
     <t>#</t>
   </si>
@@ -412,6 +412,144 @@
   </si>
   <si>
     <t>GoalUI.OptionalExperience</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>目标栏_收起</t>
+  </si>
+  <si>
+    <t>GoalUI_Collapse</t>
+  </si>
+  <si>
+    <t>GoalUI.Collapse</t>
+  </si>
+  <si>
+    <t>目标栏_展开</t>
+  </si>
+  <si>
+    <t>GoalUI_Expand</t>
+  </si>
+  <si>
+    <t>GoalUI.Expand</t>
+  </si>
+  <si>
+    <t>任务目标_适配信息</t>
+  </si>
+  <si>
+    <t>LvEnter_Grade</t>
+  </si>
+  <si>
+    <t>LvEnter.Grade</t>
+  </si>
+  <si>
+    <t>生涯记录_入口按钮</t>
+  </si>
+  <si>
+    <t>LvEnter_CareerRecord_Button</t>
+  </si>
+  <si>
+    <t>LvEnter.CareerRecord.Button</t>
+  </si>
+  <si>
+    <t>生涯记录_标题</t>
+  </si>
+  <si>
+    <t>LvEnter_CareerRecord_Title</t>
+  </si>
+  <si>
+    <t>LvEnter.CareerRecord.Title</t>
+  </si>
+  <si>
+    <t>生涯记录_已通过关卡</t>
+  </si>
+  <si>
+    <t>LvEnter_CareerRecord_ClearedLevels</t>
+  </si>
+  <si>
+    <t>LvEnter.CareerRecord.ClearedLevels</t>
+  </si>
+  <si>
+    <t>生涯记录_已通过变量试验</t>
+  </si>
+  <si>
+    <t>LvEnter_CareerRecord_ClearedExperiments</t>
+  </si>
+  <si>
+    <t>LvEnter.CareerRecord.ClearedExperiments</t>
+  </si>
+  <si>
+    <t>生涯记录_已解锁信物</t>
+  </si>
+  <si>
+    <t>LvEnter_CareerRecord_UnlockedKeepsakes</t>
+  </si>
+  <si>
+    <t>LvEnter.CareerRecord.UnlockedKeepsakes</t>
+  </si>
+  <si>
+    <t>生涯记录_成长点</t>
+  </si>
+  <si>
+    <t>LvEnter_CareerRecord_GrowthPoints</t>
+  </si>
+  <si>
+    <t>LvEnter.CareerRecord.GrowthPoints</t>
+  </si>
+  <si>
+    <t>生涯记录_印章阈值</t>
+  </si>
+  <si>
+    <t>LvEnter_CareerRecord_BadgeThresholds</t>
+  </si>
+  <si>
+    <t>LvEnter.CareerRecord.BadgeThresholds</t>
+  </si>
+  <si>
+    <t>生涯记录_最高偏移率</t>
+  </si>
+  <si>
+    <t>LvEnter_CareerRecord_MaxOffset</t>
+  </si>
+  <si>
+    <t>LvEnter.CareerRecord.MaxOffset</t>
+  </si>
+  <si>
+    <t>生涯记录_关闭</t>
+  </si>
+  <si>
+    <t>LvEnter_CareerRecord_Close</t>
+  </si>
+  <si>
+    <t>LvEnter.CareerRecord.Close</t>
+  </si>
+  <si>
+    <t>生涯结算_适配度与等级</t>
+  </si>
+  <si>
+    <t>CareerSettlement_ExperienceGrade</t>
+  </si>
+  <si>
+    <t>CareerSettlement.ExperienceGrade</t>
+  </si>
+  <si>
+    <t>生涯结算_经验明细</t>
+  </si>
+  <si>
+    <t>CareerSettlement_ExperienceBreakdown</t>
+  </si>
+  <si>
+    <t>CareerSettlement.ExperienceBreakdown</t>
+  </si>
+  <si>
+    <t>生涯结算_偏移率倍率</t>
+  </si>
+  <si>
+    <t>CareerSettlement_OffsetMultiplier</t>
+  </si>
+  <si>
+    <t>CareerSettlement.OffsetMultiplier</t>
   </si>
 </sst>
 </file>
@@ -1364,7 +1502,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.75" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1" style="1"/>
@@ -2075,6 +2213,235 @@
         <v>121</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B51" s="1">
+        <v>47</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B52" s="1">
+        <v>48</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1"/>
+      <c r="B53" s="1">
+        <v>49</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1"/>
+      <c r="B54" s="1">
+        <v>50</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1"/>
+      <c r="B55" s="1">
+        <v>51</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1"/>
+      <c r="B56" s="1">
+        <v>52</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1"/>
+      <c r="B57" s="1">
+        <v>53</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1"/>
+      <c r="B58" s="1">
+        <v>54</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1"/>
+      <c r="B59" s="1">
+        <v>55</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1"/>
+      <c r="B60" s="1">
+        <v>56</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1"/>
+      <c r="B61" s="1">
+        <v>57</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1"/>
+      <c r="B62" s="1">
+        <v>58</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1"/>
+      <c r="B63" s="1">
+        <v>59</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1"/>
+      <c r="B64" s="1">
+        <v>60</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1"/>
+      <c r="B65" s="1">
+        <v>61</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
